--- a/product_selector_out/STM32L4+ series.xlsx
+++ b/product_selector_out/STM32L4+ series.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM56"/>
+  <dimension ref="A1:BN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.8828125" customWidth="1" min="1" max="1"/>
@@ -567,7 +567,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -895,6 +896,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -990,6 +996,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1314,6 +1321,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -1641,6 +1653,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -1968,6 +1985,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2295,6 +2317,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2622,6 +2649,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -2949,6 +2981,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -3276,6 +3313,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -3603,6 +3645,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -3930,6 +3977,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -4257,6 +4309,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -4584,6 +4641,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -4911,6 +4973,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -5238,6 +5305,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -5565,6 +5637,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -5892,6 +5969,11 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -6219,6 +6301,11 @@
       </c>
       <c r="BM27" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN27" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -6546,6 +6633,11 @@
       </c>
       <c r="BM28" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN28" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -6873,6 +6965,11 @@
       </c>
       <c r="BM29" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN29" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -7200,6 +7297,11 @@
       </c>
       <c r="BM30" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN30" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -7527,6 +7629,11 @@
       </c>
       <c r="BM31" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN31" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -7854,6 +7961,11 @@
       </c>
       <c r="BM32" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN32" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -8181,6 +8293,11 @@
       </c>
       <c r="BM33" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN33" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -8508,6 +8625,11 @@
       </c>
       <c r="BM34" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN34" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -8835,6 +8957,11 @@
       </c>
       <c r="BM35" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN35" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -9162,6 +9289,11 @@
       </c>
       <c r="BM36" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN36" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -9489,6 +9621,11 @@
       </c>
       <c r="BM37" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN37" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -9816,6 +9953,11 @@
       </c>
       <c r="BM38" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN38" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -10143,6 +10285,11 @@
       </c>
       <c r="BM39" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN39" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -10470,6 +10617,11 @@
       </c>
       <c r="BM40" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN40" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4q5ag.pdf</t>
         </is>
       </c>
@@ -10797,6 +10949,11 @@
       </c>
       <c r="BM41" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN41" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -11124,6 +11281,11 @@
       </c>
       <c r="BM42" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN42" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -11451,6 +11613,11 @@
       </c>
       <c r="BM43" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN43" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -11778,6 +11945,11 @@
       </c>
       <c r="BM44" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN44" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4p5ae.pdf</t>
         </is>
       </c>
@@ -12105,6 +12277,11 @@
       </c>
       <c r="BM45" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN45" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -12432,6 +12609,11 @@
       </c>
       <c r="BM46" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN46" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -12759,6 +12941,11 @@
       </c>
       <c r="BM47" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN47" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -13086,6 +13273,11 @@
       </c>
       <c r="BM48" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN48" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -13413,6 +13605,11 @@
       </c>
       <c r="BM49" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN49" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -13740,6 +13937,11 @@
       </c>
       <c r="BM50" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN50" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -14067,6 +14269,11 @@
       </c>
       <c r="BM51" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN51" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -14394,6 +14601,11 @@
       </c>
       <c r="BM52" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN52" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -14721,6 +14933,11 @@
       </c>
       <c r="BM53" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN53" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -15048,6 +15265,11 @@
       </c>
       <c r="BM54" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN54" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
@@ -15375,6 +15597,11 @@
       </c>
       <c r="BM55" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN55" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4s5vi.pdf</t>
         </is>
       </c>
@@ -15702,12 +15929,17 @@
       </c>
       <c r="BM56" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN56" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32l4r5vi.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -15728,16 +15960,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -15750,6 +15980,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -15769,7 +16000,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -15831,7 +16064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM56"/>
+  <dimension ref="A1:BN56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -15899,6 +16132,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -16232,6 +16466,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -16327,6 +16566,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -16649,7 +16889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -16976,7 +17221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17303,7 +17553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17630,7 +17885,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -17957,7 +18217,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18284,7 +18549,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18611,7 +18881,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -18938,7 +19213,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19265,7 +19545,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19592,7 +19877,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -19919,7 +20209,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20246,7 +20541,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20573,7 +20873,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -20900,7 +21205,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21227,7 +21537,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21554,7 +21869,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM27" s="6" t="inlineStr">
+      <c r="BM27" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN27" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -21881,7 +22201,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM28" s="6" t="inlineStr">
+      <c r="BM28" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN28" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22208,7 +22533,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM29" s="6" t="inlineStr">
+      <c r="BM29" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN29" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22535,7 +22865,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM30" s="6" t="inlineStr">
+      <c r="BM30" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN30" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -22862,7 +23197,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM31" s="6" t="inlineStr">
+      <c r="BM31" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN31" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23189,7 +23529,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM32" s="6" t="inlineStr">
+      <c r="BM32" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN32" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23516,7 +23861,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM33" s="6" t="inlineStr">
+      <c r="BM33" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN33" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -23843,7 +24193,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM34" s="6" t="inlineStr">
+      <c r="BM34" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN34" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24170,7 +24525,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM35" s="6" t="inlineStr">
+      <c r="BM35" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN35" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24497,7 +24857,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM36" s="6" t="inlineStr">
+      <c r="BM36" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN36" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -24824,7 +25189,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM37" s="6" t="inlineStr">
+      <c r="BM37" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN37" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25151,7 +25521,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM38" s="6" t="inlineStr">
+      <c r="BM38" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN38" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25478,7 +25853,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM39" s="6" t="inlineStr">
+      <c r="BM39" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN39" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -25805,7 +26185,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM40" s="6" t="inlineStr">
+      <c r="BM40" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN40" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26132,7 +26517,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM41" s="6" t="inlineStr">
+      <c r="BM41" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN41" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26459,7 +26849,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM42" s="6" t="inlineStr">
+      <c r="BM42" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN42" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -26786,7 +27181,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM43" s="6" t="inlineStr">
+      <c r="BM43" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN43" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27113,7 +27513,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM44" s="6" t="inlineStr">
+      <c r="BM44" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN44" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27440,7 +27845,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM45" s="6" t="inlineStr">
+      <c r="BM45" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN45" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -27767,7 +28177,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM46" s="6" t="inlineStr">
+      <c r="BM46" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN46" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28094,7 +28509,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM47" s="6" t="inlineStr">
+      <c r="BM47" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN47" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28421,7 +28841,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM48" s="6" t="inlineStr">
+      <c r="BM48" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN48" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -28748,7 +29173,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM49" s="6" t="inlineStr">
+      <c r="BM49" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN49" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29075,7 +29505,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM50" s="6" t="inlineStr">
+      <c r="BM50" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN50" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29402,7 +29837,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM51" s="6" t="inlineStr">
+      <c r="BM51" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN51" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -29729,7 +30169,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM52" s="6" t="inlineStr">
+      <c r="BM52" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN52" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30056,7 +30501,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM53" s="6" t="inlineStr">
+      <c r="BM53" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN53" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30383,7 +30833,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM54" s="6" t="inlineStr">
+      <c r="BM54" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN54" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -30710,7 +31165,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM55" s="6" t="inlineStr">
+      <c r="BM55" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN55" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31037,7 +31497,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM56" s="6" t="inlineStr">
+      <c r="BM56" s="8" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN56" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -31045,8 +31510,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
